--- a/Presupuesto de Proyecto .xlsx
+++ b/Presupuesto de Proyecto .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B126978B-C101-43B9-BB34-F282FBE7E622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E2CC4F7-B282-43A3-B9CA-E8B5E144A1AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="74">
   <si>
     <t>Nombres: Karen Daniela Ruiz Madrigal, Juan Andres Quiceno Banoy, Juan Sebastian Delgado Inocencio, Andres Felipe Piñeros Lozano</t>
   </si>
@@ -248,7 +248,19 @@
     <t>Sacar el juego</t>
   </si>
   <si>
-    <t>D</t>
+    <t>Diseño y maquetado sitio web del juego</t>
+  </si>
+  <si>
+    <t>Programación frontend/backend web</t>
+  </si>
+  <si>
+    <t>Hosting, dominio y despliegue web</t>
+  </si>
+  <si>
+    <t>SEO y marketing digital inicial</t>
+  </si>
+  <si>
+    <t>Desarrollo web</t>
   </si>
 </sst>
 </file>
@@ -264,7 +276,7 @@
     <numFmt numFmtId="169" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="170" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -358,6 +370,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Century Gothic"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Century Gothic"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="19">
@@ -470,7 +488,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -765,12 +783,70 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1041,6 +1117,33 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2119,7 +2222,7 @@
         <v>34</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="E8" s="27">
         <v>46086</v>
@@ -2200,7 +2303,7 @@
         <v>36</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="E9" s="27">
         <v>46086</v>
@@ -2281,7 +2384,7 @@
         <v>37</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="E10" s="27">
         <v>46086</v>
@@ -2362,7 +2465,7 @@
         <v>40</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="E11" s="27">
         <v>46089</v>
@@ -2443,7 +2546,7 @@
         <v>42</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="E12" s="27">
         <v>46093</v>
@@ -2524,7 +2627,7 @@
         <v>44</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="E13" s="27">
         <v>46086</v>
@@ -2911,11 +3014,11 @@
         <v>80</v>
       </c>
       <c r="L19" s="29">
-        <v>15000</v>
+        <v>35000</v>
       </c>
       <c r="M19" s="30">
         <f>K19*L19</f>
-        <v>1200000</v>
+        <v>2800000</v>
       </c>
       <c r="N19" s="33">
         <v>0</v>
@@ -2931,11 +3034,11 @@
       </c>
       <c r="R19" s="36">
         <f t="shared" ref="R19:R20" si="4">J19+M19+N19+O19+P19</f>
-        <v>2200000</v>
+        <v>3800000</v>
       </c>
       <c r="S19" s="37">
         <f t="shared" ref="S19:S20" si="5">R19-Q19</f>
-        <v>2100000</v>
+        <v>3700000</v>
       </c>
       <c r="T19" s="8"/>
       <c r="U19" s="8"/>
@@ -2967,7 +3070,7 @@
         <v>50</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="E20" s="59">
         <v>46080</v>
@@ -2985,7 +3088,7 @@
         <v>21875</v>
       </c>
       <c r="J20" s="30">
-        <f t="shared" ref="J19:J20" si="6">H20*I20</f>
+        <f t="shared" ref="J20" si="6">H20*I20</f>
         <v>437500</v>
       </c>
       <c r="K20" s="31">
@@ -2995,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="30">
-        <f t="shared" ref="M19:M20" si="7">K20*L20</f>
+        <f t="shared" ref="M20" si="7">K20*L20</f>
         <v>0</v>
       </c>
       <c r="N20" s="33">
@@ -3125,7 +3228,7 @@
       <c r="B22" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="80" t="s">
+      <c r="C22" s="95" t="s">
         <v>68</v>
       </c>
       <c r="D22" s="26" t="s">
@@ -3141,14 +3244,14 @@
         <v>46167</v>
       </c>
       <c r="H22" s="81">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="I22" s="29">
         <v>50000</v>
       </c>
       <c r="J22" s="30">
         <f>H22*I22</f>
-        <v>2000000</v>
+        <v>4000000</v>
       </c>
       <c r="K22" s="31">
         <v>1</v>
@@ -3202,49 +3305,62 @@
     </row>
     <row r="23" spans="1:39" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8"/>
-      <c r="B23" s="41" t="s">
-        <v>45</v>
+      <c r="B23" s="96" t="s">
+        <v>73</v>
       </c>
-      <c r="C23" s="41"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="45"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="47">
-        <f>SUM(J19:J22)</f>
-        <v>4312500</v>
+      <c r="C23" s="94" t="s">
+        <v>69</v>
       </c>
-      <c r="K23" s="47"/>
-      <c r="L23" s="47"/>
-      <c r="M23" s="47">
-        <f>SUM(M19:M21)</f>
-        <v>1250000</v>
+      <c r="D23" s="26" t="s">
+        <v>61</v>
       </c>
-      <c r="N23" s="47">
-        <f>SUM(N19:N21)</f>
+      <c r="E23" s="56">
+        <v>46145</v>
+      </c>
+      <c r="F23" s="56">
+        <v>46145</v>
+      </c>
+      <c r="G23" s="56">
+        <v>46168</v>
+      </c>
+      <c r="H23" s="102">
+        <v>40</v>
+      </c>
+      <c r="I23" s="29">
+        <v>21000</v>
+      </c>
+      <c r="J23" s="30">
+        <f t="shared" ref="J23:J26" si="8">H23*I23</f>
+        <v>840000</v>
+      </c>
+      <c r="K23" s="31">
+        <v>1</v>
+      </c>
+      <c r="L23" s="29">
+        <v>25000</v>
+      </c>
+      <c r="M23" s="30">
+        <f t="shared" ref="M23:M26" si="9">K23*L23</f>
+        <v>25000</v>
+      </c>
+      <c r="N23" s="33">
         <v>0</v>
       </c>
-      <c r="O23" s="47">
-        <f>SUM(O19:O21)</f>
+      <c r="O23" s="33">
         <v>0</v>
       </c>
-      <c r="P23" s="48">
-        <f>SUM(P19:P21)</f>
+      <c r="P23" s="34">
         <v>0</v>
       </c>
-      <c r="Q23" s="49">
-        <f>SUM(Q19:Q22)</f>
-        <v>1512500</v>
+      <c r="Q23" s="34">
+        <v>1830000</v>
       </c>
-      <c r="R23" s="50">
-        <f>SUM(J23:P23)</f>
-        <v>5562500</v>
+      <c r="R23" s="34">
+        <v>1830000</v>
       </c>
-      <c r="S23" s="50">
-        <f>R23-Q23</f>
-        <v>4050000</v>
+      <c r="S23" s="37">
+        <f t="shared" ref="S23:S25" si="10">R23-Q23</f>
+        <v>0</v>
       </c>
       <c r="T23" s="8"/>
       <c r="U23" s="8"/>
@@ -3269,24 +3385,63 @@
     </row>
     <row r="24" spans="1:39" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
+      <c r="B24" s="80" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="97" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="56">
+        <v>46146</v>
+      </c>
+      <c r="F24" s="56">
+        <v>46146</v>
+      </c>
+      <c r="G24" s="56">
+        <v>46169</v>
+      </c>
+      <c r="H24" s="102">
+        <v>120</v>
+      </c>
+      <c r="I24" s="29">
+        <v>21000</v>
+      </c>
+      <c r="J24" s="30">
+        <f t="shared" si="8"/>
+        <v>2520000</v>
+      </c>
+      <c r="K24" s="31">
+        <v>1</v>
+      </c>
+      <c r="L24" s="29">
+        <v>15000</v>
+      </c>
+      <c r="M24" s="30">
+        <f t="shared" si="9"/>
+        <v>15000</v>
+      </c>
+      <c r="N24" s="33">
+        <v>0</v>
+      </c>
+      <c r="O24" s="33">
+        <v>0</v>
+      </c>
+      <c r="P24" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="34">
+        <v>2745000</v>
+      </c>
+      <c r="R24" s="34">
+        <v>2795000</v>
+      </c>
+      <c r="S24" s="37">
+        <f t="shared" si="10"/>
+        <v>50000</v>
+      </c>
       <c r="T24" s="8"/>
       <c r="U24" s="8"/>
       <c r="V24" s="8"/>
@@ -3310,26 +3465,63 @@
     </row>
     <row r="25" spans="1:39" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1" t="s">
-        <v>69</v>
+      <c r="B25" s="98" t="s">
+        <v>67</v>
       </c>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
+      <c r="C25" s="97" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25" s="56">
+        <v>46147</v>
+      </c>
+      <c r="F25" s="56">
+        <v>46147</v>
+      </c>
+      <c r="G25" s="56">
+        <v>46170</v>
+      </c>
+      <c r="H25" s="102">
+        <v>20</v>
+      </c>
+      <c r="I25" s="29">
+        <v>21000</v>
+      </c>
+      <c r="J25" s="30">
+        <f t="shared" si="8"/>
+        <v>420000</v>
+      </c>
+      <c r="K25" s="31">
+        <v>1</v>
+      </c>
+      <c r="L25" s="29">
+        <v>0</v>
+      </c>
+      <c r="M25" s="30">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="N25" s="33">
+        <v>0</v>
+      </c>
+      <c r="O25" s="33">
+        <v>0</v>
+      </c>
+      <c r="P25" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="34">
+        <v>837500</v>
+      </c>
+      <c r="R25" s="34">
+        <v>837500</v>
+      </c>
+      <c r="S25" s="37">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
       <c r="T25" s="8"/>
       <c r="U25" s="8"/>
       <c r="V25" s="8"/>
@@ -3353,24 +3545,63 @@
     </row>
     <row r="26" spans="1:39" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
-      <c r="S26" s="1"/>
+      <c r="B26" s="99" t="s">
+        <v>67</v>
+      </c>
+      <c r="C26" s="100" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E26" s="56">
+        <v>46148</v>
+      </c>
+      <c r="F26" s="56">
+        <v>46148</v>
+      </c>
+      <c r="G26" s="56">
+        <v>46171</v>
+      </c>
+      <c r="H26" s="101">
+        <v>40</v>
+      </c>
+      <c r="I26" s="29">
+        <v>21000</v>
+      </c>
+      <c r="J26" s="30">
+        <f t="shared" si="8"/>
+        <v>840000</v>
+      </c>
+      <c r="K26" s="31">
+        <v>1</v>
+      </c>
+      <c r="L26" s="29">
+        <v>0</v>
+      </c>
+      <c r="M26" s="30">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="N26" s="33">
+        <v>0</v>
+      </c>
+      <c r="O26" s="33">
+        <v>0</v>
+      </c>
+      <c r="P26" s="34">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="34">
+        <v>1075000</v>
+      </c>
+      <c r="R26" s="34">
+        <v>1075000</v>
+      </c>
+      <c r="S26" s="37">
+        <f>R26-Q26</f>
+        <v>0</v>
+      </c>
       <c r="T26" s="8"/>
       <c r="U26" s="8"/>
       <c r="V26" s="8"/>
@@ -3394,24 +3625,50 @@
     </row>
     <row r="27" spans="1:39" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
-      <c r="S27" s="1"/>
+      <c r="B27" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="41"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="43"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="45"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="47">
+        <f>SUM(J19:J22)</f>
+        <v>6312500</v>
+      </c>
+      <c r="K27" s="47"/>
+      <c r="L27" s="47"/>
+      <c r="M27" s="47">
+        <f>SUM(M19:M21)</f>
+        <v>2850000</v>
+      </c>
+      <c r="N27" s="47">
+        <f>SUM(N19:N21)</f>
+        <v>0</v>
+      </c>
+      <c r="O27" s="47">
+        <f>SUM(O19:O21)</f>
+        <v>0</v>
+      </c>
+      <c r="P27" s="48">
+        <f>SUM(P19:P21)</f>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="49">
+        <f>SUM(Q19:Q22)</f>
+        <v>1512500</v>
+      </c>
+      <c r="R27" s="50">
+        <f>SUM(J27:P27)</f>
+        <v>9162500</v>
+      </c>
+      <c r="S27" s="50">
+        <f>R27-Q27</f>
+        <v>7650000</v>
+      </c>
       <c r="T27" s="8"/>
       <c r="U27" s="8"/>
       <c r="V27" s="8"/>
@@ -43278,7 +43535,7 @@
       <formula>"Completo"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D18:D22">
+  <conditionalFormatting sqref="D18:D26">
     <cfRule type="containsText" dxfId="26" priority="16" operator="containsText" text="Approved">
       <formula>NOT(ISERROR(SEARCH(("Approved"),(D18))))</formula>
     </cfRule>
@@ -43301,7 +43558,7 @@
       <formula>NOT(ISERROR(SEARCH(("In Progress"),(D18))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D19:D22">
+  <conditionalFormatting sqref="D19:D26">
     <cfRule type="cellIs" dxfId="19" priority="23" operator="equal">
       <formula>"No Iniciado"</formula>
     </cfRule>
@@ -43327,7 +43584,7 @@
       <formula>"Completo"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S5:S14 S19:S23">
+  <conditionalFormatting sqref="S5:S14 S19:S27">
     <cfRule type="cellIs" dxfId="11" priority="31" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -43356,7 +43613,7 @@
           <x14:formula1>
             <xm:f>'listas desplegables'!$F$3:$F$11</xm:f>
           </x14:formula1>
-          <xm:sqref>D4:D13 D18:D22</xm:sqref>
+          <xm:sqref>D4:D13 D18:D26</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
